--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127473818</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>127473819</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34425-2025 artfynd.xlsx
+++ b/artfynd/A 34425-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127473823</v>
       </c>
       <c r="B2" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127473825</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>127473822</v>
       </c>
       <c r="B6" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
